--- a/chashouji/docs/闺蜜30人角色对照表.xlsx
+++ b/chashouji/docs/闺蜜30人角色对照表.xlsx
@@ -11,7 +11,7 @@
     <sheet name="说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'闺蜜30人'!$A$1:$V$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'闺蜜30人'!$A$1:$W$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -46,22 +46,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFDE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -103,12 +93,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -185,6 +169,761 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1524000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -476,31 +1215,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
     <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,3353 +1251,3389 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>形象（待机帧）</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>槽位</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>角色（名单名）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>年代</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>实际效果概述</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>进场</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>待机</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>出手</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>出手道具/飞行物</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>挂件/场景层</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>命中特效</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>站位 at [x,y,缩放]</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>角色图集（web/assets/trio/）</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>图集帧名</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>素材源目录</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>签字</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>已知小问题（非阻断）</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>名单原设计·进场</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>名单原设计·出手</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>查看链接（打开后点「闺蜜③」）</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>你的调优建议</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="125" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>7·古装</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>墨镜短发比基尼（原创）</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>老角色（原样保留）：头顶墨镜、条纹比基尼，踩粉色平衡车从左边滑进来刹停；举防狼喷雾摇罐，对着他的脸"呲—呲—"连喷，喷口跟着他的脸转</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>骑行滑入（帧：ride→brake→idle）</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>连续喷射（帧：wind→aim→follow）</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>pepper（喷雾雾团）</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>[70,880,0.8]</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>G1_shades.webp</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>idle wind follow ride brake aim0 aim1 aim2 aim3 aim4 aim5 aim6 aim7 aim8 aim9 aim10 kick0 kick1 kick2 kick3 kick4 kick5 kick6 kick7 kick8 kick9 kick10</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G1_shades</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>已签·第九批</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>平衡车</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>防狼喷雾</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G1.G11.G24</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr"/>
+      <c r="W2" s="4" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="125" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>8·仙侠</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>蓝发发明家（布尔玛式）</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>老角色（原样保留）：蓝发发明家，踩平衡车滑进来刹停；举自制喷雾器对他的脸连喷，喷口跟着他的脸转</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>骑行滑入（帧：ride→brake→idle）</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>连续喷射（帧：wind→aim→follow）</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>pepper（喷雾雾团）</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>[90,890,0.8]</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>G2_bulma.webp</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>idle wind follow ride brake aim0 aim1 aim2 aim3 aim4 aim5 aim6 aim7 aim8 aim9 aim10 kick0 kick1 kick2 kick3 kick4 kick5 kick6 kick7 kick8 kick9 kick10</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G2_bulma</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>已签·第九批</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>平衡车</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>自制喷雾器</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G2.G13.G29</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="4" ht="125" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>10·少女</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>月光水手（美少女战士式）</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>老角色（原样保留）：月光水手少女，踩平衡车滑进来刹停；举喷雾对他的脸连喷，喷口跟着他的脸转</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>骑行滑入（帧：ride→brake→idle）</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>连续喷射（帧：wind→aim→follow）</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>pepper（喷雾雾团）</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>[80,880,0.8]</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>G3_sailor.webp</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>idle wind follow ride brake aim0 aim1 aim2 aim3 aim4 aim5 aim6 aim7 aim8 aim9 aim10 kick0 kick1 kick2 kick3 kick4 kick5 kick6 kick7 kick8 kick9 kick10</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G3_sailor</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>已签·第九批</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>平衡车</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>喷雾</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G3.G12.G27</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="5" ht="125" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>1·格斗</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>丸子头旗袍格斗家（春丽式）</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>倒立劈叉旋转踢从左边转进来、落地一蹲、站成格斗架；百裂脚 —— 右腿高踢连踢，一串腿影从女生头顶翻过去砸他</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>翻滚进场（帧：spin1→spin2→spin1→land→idle）</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>冲上去连击（帧：wind→hitA,hitB→follow）</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>star（金星）</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>[190,980,0.82]</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>G4_chunli.webp</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>idle wind hitA hitB spin1 spin2 land follow</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G4_chunli</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>已签·第五批</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>倒立旋转踢转进来</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>百裂脚：一串腿影</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G4.G17.G21</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="125" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2·客栈</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>客栈老板娘（佟湘玉式）</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>腰侧挂着大算盘、叉着腰扭着走进来，惊呼"额滴神"；摘下算盘举过头顶，一把 3D 算盘甩出去砸他</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>走进来（帧：walk1,walk2,walk3,walk4）</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>abacus：prop_abacus.webp</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>G5_abacus.webp(随出手消失)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>debris（碎屑），命中后 bounce</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>[150,980,0.84]</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>G5_tong.webp</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow walk1 walk2 walk3 walk4</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G5_tong</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>已签·第十批</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>扭着腰走进来，手拍算盘</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>甩算盘珠子，喊"额滴神"</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G5.G15.G23</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="7" ht="125" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>3·妈妈辈</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>平底锅主妇（蜡笔小新妈式）</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>额头冒青筋、围裙拖鞋气冲冲跑进来，攥着平底锅；把锅举过头顶抡出去，3D 平底锅"当"地砸在他头上</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>走进来（帧：walk1,walk2,walk3,walk4）</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>pan：prop_pan.webp</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>thud（闷击冲击圈），命中后 bounce</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>[170,980,0.88]</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>G6_misae.webp</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow walk1 walk2 walk3 walk4</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G6_misae</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>已签·第五批</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>walk3 腰侧 6 px 绿线（非阻断）</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>围裙拖鞋气冲冲冲进来</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>扔平底锅（3D），打中"当"一声</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G6.G20.G30</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="125" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>G7</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>4·暗杀</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>黑裙荆棘杀手（约尔式）</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>一团暗紫黑烟里蹲着现身、起身撩发，温柔地笑；手指夹着玫瑰护手的细刺刀举过头顶甩出去</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>原地显现（帧：crouch→rise→emerge→idle）</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>knife：world/trio_g7_knife.webp</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>petal（花瓣），命中后 bounce</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>[220,960,0.88]</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>G7_yor.webp</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow crouch rise emerge idle2</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G7_yor</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>已签·第九批</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>从阴影里一闪出现</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>甩飞刀 / 细长刺</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G7.G16.G26</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="9" ht="125" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>G8</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>5·女王</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>冰雪女王（艾莎式：白金侧麻花辫、冰蓝长裙）</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>踮着脚一路滑冰滑进来（燕式滑行 → 踮脚转一圈 → 急停），掌心上浮着一根冰锥；把冰锥举过头顶一掷，打中他的头冻出一层冰壳</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>骑行滑入（帧：glide→twirl→stop→idle）</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>icicle：world/trio_g8_icicle.webp</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>G8_snowflake.webp</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>water（水花），命中后 freeze</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>[200,960,0.81]</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>G8_elsa.webp</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow glide twirl stop idle2</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G8_elsa</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>已签·第八批</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>脚下结冰没做（非阻断）；冰锥飞行 0.16 秒过 G18 膝前（不阻断，待办）</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>脚下一路结冰，滑冰滑进来</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>甩冰锥，打中冻出一层冰花</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G8.G18.G25</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr"/>
     </row>
-    <row r="10">
+    <row r="10" ht="125" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>6·广场</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>广场舞大妈（花衬衫、红绸、腰挂小音箱）</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>腰挂小音箱、扭着秧歌步抬腿甩手走进来；一只手叉腰、一只手翘着兰花指打拍子；抡起一条红绸从头顶甩过去抽他</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>走进来（帧：walk1,walk2,walk3,walk4）</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>甩鞭/绸抽打（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>rouge（红粉/口红印）</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>[170,970,0.88]</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>G9_auntie.webp</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow walk1 walk2 walk3 walk4</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G9_auntie</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>已签·第八批</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>音波圈没做（非阻断）</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>扭秧歌步进来</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>甩红绸 + 小音箱音波圈</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G9.G19.G28</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="inlineStr"/>
     </row>
-    <row r="11">
+    <row r="11" ht="125" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>G10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>后排地面</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>9·女英雄</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>粉蓝双马尾坏女孩（小丑女式：发尾一边粉一边蓝、棒球棍）</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>踩着红蓝轮滑压低身子冲进来、单脚一转、横刹停住；球棒扛在肩上吐舌头，举过头顶抡出去（3D 棒球棍打着转飞）</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>骑行滑入（帧：cruise→spin→stop→idle）</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>bat：prop_bat_v2.webp</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>G10_bat.webp(随出手消失)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>star（金星），命中后 bounce</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>[160,1020,0.86]</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>G10_harley.webp</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow cruise spin stop idle2</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G10_harley</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>已签·第十一批（挪位复核）</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>扔出后空拳约 1.5 秒（非阻断）</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>踩轮滑滑进来一个转身</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>甩棒球棍旋转飞过去，打中蹦“BAM”字</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G10.G14.G22</t>
         </is>
       </c>
-      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="125" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>G11</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>7·古装</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>花饰格格（小燕子式）</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>秋千从左上画外荡进来（往前荡伸腿、往后荡收腿），荡到最前面抛绣球砸他的头</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>荡秋千进场（帧：tuck→kick）</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>帧 idle +秋千摆 +引擎画绳，呼吸起伏</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：raise→wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>ball：world/trio_prop_ball.webp</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>G11_tassel.webp</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>petal（花瓣），命中后 bounce</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>[170,480,1]</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>G11_gege.webp</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>idle raise throw follow wind tuck kick idle2</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>—（引擎维护）</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>已签·样板第二轮；第十批复核配方</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>秋千荡进来</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>抛绣球</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G1.G11.G24</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" ht="125" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>G12</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>10·少女</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>紫衣仙子（紫霞式）</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>秋千从左上画外荡进来，飞吻，爱心打到他脸上留下口红印（查岗证据）</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>荡秋千进场（帧：idle）</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>帧 idle +秋千摆 +引擎画绳，呼吸起伏</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：kiss→idle）</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>heart：程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>rouge（红粉/口红印），命中后 lips</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>[165,210,1]</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>G12_fairy.webp</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>idle kiss</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G12_fairy</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>已签·第九批</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>秋千荡进来</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>飞吻口红印</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G3.G12.G27</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" ht="125" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>G13</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>8·仙侠</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>白衣古墓仙子（小龙女式）</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>躺在一根横拉的麻绳上从左边滑进来、随绳颠着荡；支起身子一甩白绸，绸梢金铃"叮当"抽过去</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>躺绳上荡入（帧：follow→idle）</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>甩鞭/绸抽打（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>G13_peg.webp(场景层)</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>star（金星）</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>[175,500,0.66]</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>G13_xiaolongnv.webp</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G13_xiaolongnv</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>已签·第十一批</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>躺在一根横拉的绳子上荡进来</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>金铃索：白绸带末端金铃抽过去，叮当</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G2.G13.G29</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" ht="125" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>G14</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>9·女英雄</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>金发剑之公主（希瑞式：金色长发头冠、红披风，白短战裙面积压小）</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>左上一道蓝白闪光里举剑变身现身，剑指前方、扛剑站定；双手举剑过头一劈，金色剑光斩在他身上</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>原地显现（帧：wind→follow→idle）</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>剑光斩（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>G14_ledge.webp(场景层)</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>star（金星）</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>[170,520,0.7]</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>G14_shera.webp</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G14_shera</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>已签·第十一批</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>名单"闪电劈下"是白色十字闪光（非阻断，第九批已记）</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>左上举剑一道闪电劈下，变身出现</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>金色剑光劈过去</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G10.G14.G22</t>
         </is>
       </c>
-      <c r="V15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" ht="125" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>G15</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2·客栈</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>船头红发少女（泰坦尼克 Rose 式：红卷发、复古长裙）</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>站在一截白色船头上从左边平着滑出来，捂着心口 → 张开双臂"飞"；举起心形蓝宝石项链一抛（3D）砸他</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>飞入/降下（帧：follow→open→idle）</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>necklace：prop_necklace.webp</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>water（水花），命中后 bounce</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>[190,545,0.75]</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>G15_rose.webp</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow grip step open idle2</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G15_rose</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>已签·第九批</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>站在一截船头上从左上滑出，张开双臂</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>扔心形蓝宝石项链（3D，闪蓝光）</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G5.G15.G23</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="125" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>G16</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>4·暗杀</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>狐尾妖姬（妲己式）</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>一团狐火橙烟里九条白尾巴裹着她现身，伸个懒腰、托腮一笑；掌心托一团青蓝狐火，举过头顶甩出去</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>原地显现（帧：wrap→stretch→lean→idle）</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>foxfire：world/trio_g16_foxfire.webp</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>foxfire（青蓝狐火），命中后 bounce</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>[275,550,0.8]</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>G16_daji.webp</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow wrap stretch lean idle2</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G16_daji</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>已签·第十一批（挪位复核）</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>九尾托着坐在左上</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>青蓝狐火球 + 尾巴一扫</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G7.G16.G26</t>
         </is>
       </c>
-      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" ht="125" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>G17</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>1·格斗</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>粉绿麻花辫恋柱（甘露寺式）</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>脚踝拴着绳从左上倒挂着掉下来、弹两下，捧着脸颊笑；握着剑柄一甩，粉色软鞭剑螺旋着抽过去，打中迸樱花瓣</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>倒挂落下（帧：plunge→bounce→settle→idle）</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>甩鞭/绸抽打（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>petal（花瓣）</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>[150,240,1.06]</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>G17_mitsuri.webp</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow plunge bounce settle idle2</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G17_mitsuri</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>已签·第八批</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>从左上倒挂垂下</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>粉色软鞭剑螺旋甩出，鞭痕带樱花瓣</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G4.G17.G21</t>
         </is>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="19" ht="125" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>G18</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>5·女王</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>挂帅女将（穆桂英式京剧武旦：背插四面靠旗、头顶两根长翎子、大红金边女靠）</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>从左上一跃落下、单膝点地，起身亮相，翎子一甩；红缨枪举过头顶掷出去（3D）</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>跃起落下（帧：leap→land→rise→idle）</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>spear：prop_spear.webp</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>G18_ledge.webp(场景层)，G18_flags.webp，G18_feathers.webp</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>petal（花瓣），命中后 bounce</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>[496,640,0.88]</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>G18_mu.webp</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow leap land rise idle2</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G18_mu</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>已签·第十一批（挪位 + 跨边复核）</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>从左上一跃落下，单膝落在墙沿，翎子一甩亮相</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>甩出红缨枪旋转飞过去，命中时红缨炸开成一朵红花</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G8.G18.G25</t>
         </is>
       </c>
-      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="inlineStr"/>
     </row>
-    <row r="20">
+    <row r="20" ht="125" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>G19</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>6·广场</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>网红主播（坐无人机上直播）</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>戴猫耳耳机、举着手机直播，坐着白色四旋翼无人机从左边飞进来（前倾冲 → 后仰急刹 → 挥手打招呼）；甩出一枚打赏小火箭（3D）砸他</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>飞入/降下（帧：zoom→brake→wave）</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>rocket：prop_rocket.webp</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>G19_drone.webp</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>star（金星），命中后 bounce</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>[160,460,0.9]</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>G19_streamer.webp</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow zoom brake wave idle2</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G19_streamer</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>已签·第八批</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>缺 confetti 配方、桨叶不转（非阻断）</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>坐着无人机飞进来</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>举手机直播，甩出打赏小火箭，打中炸彩纸</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G9.G19.G28</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="inlineStr"/>
     </row>
-    <row r="21">
+    <row r="21" ht="125" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>G20</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>3·妈妈辈</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>复古歌后（邓丽君式旗袍卷发）</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>坐在一弯金月亮上从正上方缓缓降下来，挥手 → 张开双臂唱 → 坐定捂心口轻唱；指尖捏一枚月牙镖举过头顶一弹，打着转飞过去</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>飞入/降下（帧：wave→sing→idle）</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>crescent：world/trio_g20_crescent.webp</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>G20_moon.webp</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>crescent（金月牙+音符），命中后 bounce</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>[110,480,0.9]</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>G20_teresa.webp</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow wave sing bow idle2</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G20_teresa</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>已签·第十一批（挪位复核）</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>坐在月亮道具上降下来</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>甩出一弯小月牙飞镖，拖音符尾</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G6.G20.G30</t>
         </is>
       </c>
-      <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" s="4" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="22" ht="125" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>G21</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>1·格斗</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>忍者扇娘（不知火舞式）</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>左下角翻滚进来（团身滚 → 落地蹲 → 半跪），胸罩当手里剑甩出去，打中挂在他头上</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>翻滚进场（帧：roll→land→idle）</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind0→wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>bra：world/trio_prop_bra.webp</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>rouge（红粉/口红印），命中后 wear</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>[150,1310,1]</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>G21_mai.webp</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>idle wind0 throw follow roll land wind idle2</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G21_mai</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>已签·第三批（维持）</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>翻滚进来半跪</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>胸罩手里剑</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G4.G17.G21</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="23" ht="125" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>G22</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>9·女英雄</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>麻花辫探险家（劳拉式）</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>左下角匍匐爬进来（左右肘交替）趴定，举相机拍照取证，闪光晃他的眼，照片飞出来</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>匍匐爬入（帧：crawl1→crawl2→crawl1→crawl2→land→idle）</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>拍照闪光（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>G22_legs.webp</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>star（金星）</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>[200,1314,1]</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>G22_explorer.webp</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow crawl1 crawl2 land idle2</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G22_explorer</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>已签·第三批</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>匍匐爬进来</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>拍照取证</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G10.G14.G22</t>
         </is>
       </c>
-      <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="24" ht="125" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>G23</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2·客栈</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>客栈女侠（郭芙蓉式）</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>马步从左下角滑进来、跺地站定，排山倒海 —— 双掌齐推，一道气浪轰他的脸</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>滑入（帧：slide→land→idle）</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>光束/气浪（帧：raise→throw→follow）</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>thud（闷击冲击圈）</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>[175,1330,1]</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>G23_furong.webp</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>idle raise throw follow slide land wind idle2</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G23_furong</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>已签·第三批</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>一个马步滑进来</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>排山倒海：推掌气浪</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G5.G15.G23</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" ht="125" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>G24</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>7·古装</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>宫斗贵妃（华妃式）</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>侧卧着从左下角滑进来、撑肘起身扶正旗头，弹出一枚金护甲砸他 —— 赏"一丈红"（打中炸红粉）</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>滑入（帧：slide→land→idle）</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>nailguard：world/trio_g24_nailguard.webp</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>rouge（红粉/口红印），命中后 bounce</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>[280,1325,1]</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>G24_huafei.webp</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow slide land wind2 idle2</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G24_huafei</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>已签·第三批（维持）</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>被宫女扶着跪坐 / 侧卧</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>扔护甲指套，赏"一丈红"</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G1.G11.G24</t>
         </is>
       </c>
-      <c r="V25" s="4" t="inlineStr"/>
+      <c r="W25" s="4" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="26" ht="125" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>G25</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>5·女王</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>大针筒护士</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>踩着输液架轮座从左下角滑进来、跳下来半跪扶着输液架，甩一支巨型针筒飞镖，扎在他头上</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>滑入（帧：ride→hop→idle）</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>syringe：prop_syringe.webp，world/trio_g25_syringe.webp</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>rouge（红粉/口红印），命中后 wear</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>[185,1330,1]</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>G25_nurse.webp</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow ride hop wind2 idle2</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G25_nurse</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>已签·第三批</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>推着输液架滑进来</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>巨型针筒飞镖</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G8.G18.G25</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="4" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" ht="125" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>G26</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>4·暗杀</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>蝴蝶发饰剑士（蝴蝶忍式）</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>从左上轻轻一跃、张开蝴蝶羽织落地蹲下，挥袖放出一群毒蝴蝶扑过去</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>跃起落下（帧：leap→land→idle）</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>帧 idle +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind2→throw→follow）</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>butterfly：prop_butterfly.webp</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>petal（花瓣）</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>[175,1330,1]</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>G26_shinobu.webp</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow leap land wind2 idle2</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G26_shinobu</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>已签·第三批</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>蝴蝶群散角（非阻断）</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
         <is>
           <t>轻跳落地半蹲</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>毒蝴蝶群扑过去</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G7.G16.G26</t>
         </is>
       </c>
-      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="28" ht="125" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>G27</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>10·少女</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>暴脾气平民女孩（杉菜式）</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>从左下角冲过来一记滑铲、撑地起身半跪，抡起书包砸过去</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>滑入（帧：tackle→rise→idle）</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>schoolbag：prop_schoolbag.webp</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>thud（闷击冲击圈），命中后 bounce</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>[170,1330,1]</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>G27_shancai.webp</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow tackle rise wind2 idle2</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G27_shancai</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>已签·第五批</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>冲过来滑铲</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>抡书包砸过去</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G3.G12.G27</t>
         </is>
       </c>
-      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="inlineStr"/>
     </row>
-    <row r="29">
+    <row r="29" ht="125" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>G28</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>6·广场</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>80 年代健美操女（发带、荧光紧身衣、腿套）</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>从左边一路开合跳进来，指尖转着呼啦圈，甩出去套在他头上</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>走进来（帧：jump1,jump2,jump3,jump4）</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>投掷飞行道具（帧：wind→throw→jump3）</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>hoop：prop_hoop.webp，world/trio_g28_hoop.webp</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>star（金星），命中后 wear</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>[155,1330,0.9]</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>G28_aerobics.webp</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow jump1 jump2 jump3 jump4</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G28_aerobics</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>已签·第五批</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>一路开合跳进来</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>甩荧光呼啦圈（3D）套住他</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G9.G19.G28</t>
         </is>
       </c>
-      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="125" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>G29</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>8·仙侠</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>打狗棒女侠（黄蓉式）</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>撑着打狗棒从左上一跃、棒子点地荡进来落成蹲，竹棒伸缩着捅过去</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>跃起落下（帧：vault→swing→land→idle）</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>帧 idle，呼吸起伏</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>伸缩捅击（帧：wind→throw→wind）</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>G29_staff.webp</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>thud（闷击冲击圈）</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>[180,1328,0.98]</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>G29_huangrong.webp</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow vault swing land idle2</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G29_huangrong</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>已签·第三批；棒点地第十一批实拍</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>棒点地**未解**：swing 棒尖随人滑约 130 px、不着地（非阻断，待办）</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>撑打狗棒一跃，棒点地荡进来落成蹲</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>打狗棒捅过去（伸缩，像橡皮拳）</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G2.G13.G29</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="inlineStr"/>
     </row>
-    <row r="31">
+    <row r="31" ht="125" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>G30</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>前景地板</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>3·妈妈辈</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>葫芦山蛇精式妖女（绿衣、蛇形高髻、如意）</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>像蛇一样左右扭着从左下角滑进来、斜倚坐起，举如意放一道绿光吸住他</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>滑入（帧：slither1→slither2→slither1→slither2→follow）</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>帧 follow +局部摆动flex，呼吸起伏</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>光束/气浪（帧：wind2→wind→throw→follow）</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>程序绘制（引擎画）</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>star（金星）</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>[200,1332,1]</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>G30_snake.webp</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>idle wind throw follow slither1 slither2 wind2 idle2</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>v14/trio/bestie/G30_snake</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>已签·第三批</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>螺旋光 / 命中金星（非阻断）</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
         <is>
           <t>像蛇一样扭着滑进来</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>举如意放一道绿色螺旋光把他吸住</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>http://1.14.252.30:40235/index.html?bestie=G6.G20.G30</t>
         </is>
       </c>
-      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V31"/>
+  <autoFilter ref="A1:W31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
